--- a/data/trans_bre/P1427-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1427-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,78</t>
+          <t>-0,59</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-29,09%</t>
+          <t>-23,11%</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,06</t>
+          <t>-2,83; 0,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,16</t>
+          <t>-0,7; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,7</t>
+          <t>-2,18; 0,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,24; 797,66</t>
+          <t>-71,28; 949,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 40,88</t>
+          <t>-63,33; 46,11</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -714,22 +714,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,81</t>
+          <t>-2,64; 1,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,51</t>
+          <t>-1,29; 1,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,69</t>
+          <t>-1,37; 1,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 372,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 115,69</t>
+          <t>-50,75; 136,52</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>206,51%</t>
+          <t>106,59%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,66</t>
+          <t>-3,01; 0,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 4,73</t>
+          <t>-1,73; 4,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,5</t>
+          <t>0,45; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,4</t>
+          <t>-89,83; 73,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-68,41; 315,44</t>
+          <t>-72,92; 322,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,98; 1167,22</t>
+          <t>10,01; 322,51</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-42,31%</t>
+          <t>-26,05%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,17</t>
+          <t>-2,48; 0,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,76</t>
+          <t>0,47; 2,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,43</t>
+          <t>-2,35; 0,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-74,02; 13,28</t>
+          <t>-71,63; 13,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,69; 725,21</t>
+          <t>41,98; 774,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,55; -13,25</t>
+          <t>-49,34; 8,33</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,48</t>
+          <t>0,23; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,82</t>
+          <t>-0,32; 2,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,94</t>
+          <t>0,72; 4,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 475,91</t>
+          <t>1,36; 485,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 281,33</t>
+          <t>-18,76; 268,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 115,06</t>
+          <t>12,09; 132,15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>626,89%</t>
+          <t>610,74%</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,86</t>
+          <t>3,24; 5,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,69</t>
+          <t>1,59; 3,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,4</t>
+          <t>3,1; 6,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>132,22; 2883,56</t>
+          <t>112,16; 2747,56</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,47</t>
+          <t>-0,08; 1,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,85</t>
+          <t>0,64; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 2,11</t>
+          <t>0,6; 1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 91,34</t>
+          <t>-4,52; 87,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,15; 226,42</t>
+          <t>47,65; 234,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 80,51</t>
+          <t>17,19; 71,13</t>
         </is>
       </c>
     </row>
